--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260802_204240.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260802_204240.xlsx
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260802_204240.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260802_204240.xlsx
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
